--- a/boss_pack/sme_dual_engine_boss_pack.xlsx
+++ b/boss_pack/sme_dual_engine_boss_pack.xlsx
@@ -189,7 +189,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://github.com/RnDprincipiacapital/SME-Dual_Engine/blob/main/samples/galway-sme-dashboard-expanded-public.json</t>
+          <t>https://rndprincipiacapital.github.io/sme-dual-engine-public/targets.json</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://github.com/RnDprincipiacapital/SME-Dual_Engine/blob/main/samples/galway-sme-dashboard-expanded-public.json</t>
+          <t>https://rndprincipiacapital.github.io/sme-dual-engine-public/targets.json</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://github.com/RnDprincipiacapital/SME-Dual_Engine/blob/main/samples/galway-sme-dashboard-expanded-public.json</t>
+          <t>https://rndprincipiacapital.github.io/sme-dual-engine-public/targets.json</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://github.com/RnDprincipiacapital/SME-Dual_Engine/blob/main/samples/galway-sme-dashboard-expanded-public.json</t>
+          <t>https://rndprincipiacapital.github.io/sme-dual-engine-public/targets.json</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://github.com/RnDprincipiacapital/SME-Dual_Engine/blob/main/samples/galway-sme-dashboard-expanded-public.json</t>
+          <t>https://rndprincipiacapital.github.io/sme-dual-engine-public/targets.json</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://github.com/RnDprincipiacapital/SME-Dual_Engine/blob/main/samples/galway-sme-dashboard-expanded-public.json</t>
+          <t>https://rndprincipiacapital.github.io/sme-dual-engine-public/targets.json</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -7479,7 +7479,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:O43"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
@@ -7495,6 +7495,7 @@
     <col min="12" max="12" width="34" customWidth="1"/>
     <col min="13" max="13" width="42" customWidth="1"/>
     <col min="14" max="14" width="42" customWidth="1"/>
+    <col min="15" max="15" width="42" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7579,6 +7580,11 @@
       </c>
       <c r="N3" t="inlineStr" s="2">
         <is>
+          <t>Source Note</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr" s="2">
+        <is>
           <t>Report Href</t>
         </is>
       </c>
@@ -7647,6 +7653,11 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-airflow-air-refrigeration-galway-galway/ic_draft.html</t>
         </is>
       </c>
@@ -7715,6 +7726,11 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-pat-kelly-plumbing-and-heating-contractors-galway-galway/ic_draft.html</t>
         </is>
       </c>
@@ -7783,6 +7799,11 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-coen-steel-galway/ic_draft.html</t>
         </is>
       </c>
@@ -7851,6 +7872,11 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-ideal-installation-construction-galway/ic_draft.html</t>
         </is>
       </c>
@@ -7919,6 +7945,11 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-stationery-supplies-galway/ic_draft.html</t>
         </is>
       </c>
@@ -7987,6 +8018,11 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-kevin-walsh-plumbing-galway-galway/ic_draft.html</t>
         </is>
       </c>
@@ -8055,6 +8091,11 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-stainless-steel-galway/ic_draft.html</t>
         </is>
       </c>
@@ -8123,6 +8164,11 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-bellville-building-construction-galway-galway/ic_draft.html</t>
         </is>
       </c>
@@ -8191,6 +8237,11 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-spellman-construction-claregalway-galway/ic_draft.html</t>
         </is>
       </c>
@@ -8259,6 +8310,11 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-primary-care-galway-city-east-health-centre-galway/ic_draft.html</t>
         </is>
       </c>
@@ -8327,6 +8383,11 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-grealish-gas-fuel-galway-galway/ic_draft.html</t>
         </is>
       </c>
@@ -8395,6 +8456,11 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-greaney-glass-products-galway/ic_draft.html</t>
         </is>
       </c>
@@ -8463,6 +8529,11 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-claregalway-logistics-galway/ic_draft.html</t>
         </is>
       </c>
@@ -8531,6 +8602,11 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-east-galway-quality-tool-hire-galway/ic_draft.html</t>
         </is>
       </c>
@@ -8599,6 +8675,11 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-complete-roofing-galway/ic_draft.html</t>
         </is>
       </c>
@@ -8667,6 +8748,11 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-l-zinc-roofing-galway/ic_draft.html</t>
         </is>
       </c>
@@ -8735,6 +8821,11 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-tool-and-mould-galway/ic_draft.html</t>
         </is>
       </c>
@@ -8803,6 +8894,11 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-o-malley-construction-claregalway-no-1-galway/ic_draft.html</t>
         </is>
       </c>
@@ -8871,6 +8967,11 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-truck-centre-galway/ic_draft.html</t>
         </is>
       </c>
@@ -8939,6 +9040,11 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-iclean-professional-cleaning-services-galway/ic_draft.html</t>
         </is>
       </c>
@@ -9007,6 +9113,11 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-car-care-galway/ic_draft.html</t>
         </is>
       </c>
@@ -9075,6 +9186,11 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-oven-cleaning-galway/ic_draft.html</t>
         </is>
       </c>
@@ -9143,6 +9259,11 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-james-cunningham-heating-contractors-galway-galway/ic_draft.html</t>
         </is>
       </c>
@@ -9211,6 +9332,11 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-maintenance-galway/ic_draft.html</t>
         </is>
       </c>
@@ -9279,6 +9405,11 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-specsavers-hearcare-galway/ic_draft.html</t>
         </is>
       </c>
@@ -9347,6 +9478,11 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-desmond-murphy-truck-sales-galway-galway/ic_draft.html</t>
         </is>
       </c>
@@ -9415,6 +9551,11 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-j-o-toole-sons-galway-galway/ic_draft.html</t>
         </is>
       </c>
@@ -9483,6 +9624,11 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-healy-electrical-galway-galway/ic_draft.html</t>
         </is>
       </c>
@@ -9551,6 +9697,11 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-tool-mould-innovations-galway/ic_draft.html</t>
         </is>
       </c>
@@ -9619,6 +9770,11 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-fuel-supplies-galway/ic_draft.html</t>
         </is>
       </c>
@@ -9687,6 +9843,11 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-tuam-road-galway-service-station-galway/ic_draft.html</t>
         </is>
       </c>
@@ -9755,6 +9916,11 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-east-galway-tyres-galway/ic_draft.html</t>
         </is>
       </c>
@@ -9823,6 +9989,11 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-electrical-services-galway/ic_draft.html</t>
         </is>
       </c>
@@ -9891,6 +10062,11 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-truck-and-van-testing-centre-galway/ic_draft.html</t>
         </is>
       </c>
@@ -9959,6 +10135,11 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
           <t>ic_packs/name-county-galway-catering-galway/ic_draft.html</t>
         </is>
       </c>
@@ -9979,12 +10160,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t/>
+          <t>Construction &amp; Built Environment</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Diversified Support Services</t>
+          <t>Roofing &amp; cladding</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -10022,10 +10203,15 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://services.cro.ie/cws/company/711992/C?format=json</t>
+          <t/>
         </is>
       </c>
       <c r="N39" t="inlineStr">
+        <is>
+          <t>CRO evidence available; search company name/number manually in CRO if required.</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>ic_packs/cro-711992/ic_draft.html</t>
         </is>
@@ -10047,12 +10233,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t/>
+          <t>Construction &amp; Built Environment</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Diversified Support Services</t>
+          <t>Roofing &amp; cladding</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -10090,10 +10276,15 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://services.cro.ie/cws/company/786116/C?format=json</t>
+          <t/>
         </is>
       </c>
       <c r="N40" t="inlineStr">
+        <is>
+          <t>CRO evidence available; search company name/number manually in CRO if required.</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
         <is>
           <t>ic_packs/cro-786116/ic_draft.html</t>
         </is>
@@ -10115,12 +10306,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t/>
+          <t>Construction &amp; Built Environment</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Diversified Support Services</t>
+          <t>Roofing &amp; cladding</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -10158,10 +10349,15 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://services.cro.ie/cws/company/59625/C?format=json</t>
+          <t/>
         </is>
       </c>
       <c r="N41" t="inlineStr">
+        <is>
+          <t>CRO evidence available; search company name/number manually in CRO if required.</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
         <is>
           <t>ic_packs/cro-59625/ic_draft.html</t>
         </is>
@@ -10183,12 +10379,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t/>
+          <t>Construction &amp; Built Environment</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Diversified Support Services</t>
+          <t>Roofing &amp; cladding</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -10226,10 +10422,15 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://services.cro.ie/cws/company/222180/C?format=json</t>
+          <t/>
         </is>
       </c>
       <c r="N42" t="inlineStr">
+        <is>
+          <t>CRO evidence available; search company name/number manually in CRO if required.</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
         <is>
           <t>ic_packs/cro-222180/ic_draft.html</t>
         </is>
@@ -10251,12 +10452,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t/>
+          <t>Construction &amp; Built Environment</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Diversified Support Services</t>
+          <t>Roofing &amp; cladding</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -10294,17 +10495,22 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://services.cro.ie/cws/company/698394/C?format=json</t>
+          <t/>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
+          <t>CRO evidence available; search company name/number manually in CRO if required.</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
           <t>ic_packs/cro-698394/ic_draft.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N43"/>
+  <autoFilter ref="A3:O43"/>
 </worksheet>
 </file>
 
@@ -10321,7 +10527,7 @@
     <col min="7" max="7" width="25" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="35" customWidth="1"/>
-    <col min="10" max="10" width="38" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
     <col min="11" max="11" width="25" customWidth="1"/>
     <col min="12" max="12" width="42" customWidth="1"/>
     <col min="13" max="13" width="42" customWidth="1"/>
@@ -10393,7 +10599,7 @@
       </c>
       <c r="J3" t="inlineStr" s="2">
         <is>
-          <t>Gics Industry Group</t>
+          <t>Subsector</t>
         </is>
       </c>
       <c r="K3" t="inlineStr" s="2">
@@ -10469,27 +10675,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Businesses</t>
+          <t>Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Homecare &amp; nursing agencies</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>public profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Public profile has contact/trading evidence but no explicit sale signal.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Public profile has contact/trading evidence but no explicit sale signal.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -10555,7 +10761,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -10636,7 +10842,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Plumbing &amp; drainage</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -10717,7 +10923,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Steel fabrication &amp; metalwork</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -10798,7 +11004,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Real Estate Management &amp; Development</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -10879,7 +11085,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Farm machinery &amp; agri services</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -10955,27 +11161,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>public profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Public profile has contact/trading evidence but no explicit sale signal.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Public profile has contact/trading evidence but no explicit sale signal.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -11041,7 +11247,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -11122,7 +11328,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Farm machinery &amp; agri services</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -11203,7 +11409,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Real Estate Management &amp; Development</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -11284,7 +11490,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -11365,7 +11571,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -11446,7 +11652,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -11527,7 +11733,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -11608,7 +11814,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Plant &amp; equipment maintenance</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -11684,12 +11890,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Commercial Nurseries</t>
+          <t>Retail &amp; Consumer</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Garden centres &amp; nurseries</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -11770,7 +11976,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -11851,7 +12057,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Plumbing &amp; drainage</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -11932,7 +12138,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Steel fabrication &amp; metalwork</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -12013,7 +12219,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -12094,7 +12300,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -12175,7 +12381,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12256,7 +12462,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12332,27 +12538,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>agri_food</t>
+          <t>Food &amp; Agribusiness</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Agricultural supply &amp; co-ops</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>public profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Public profile has contact/trading evidence but no explicit sale signal.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Public profile has contact/trading evidence but no explicit sale signal.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -12413,12 +12619,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Landscaping / Grounds Services</t>
+          <t>Construction &amp; Built Environment</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Landscaping &amp; grounds maintenance</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -12494,12 +12700,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Landscaping / Grounds Services</t>
+          <t>Construction &amp; Built Environment</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Landscaping &amp; grounds maintenance</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12580,7 +12786,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -12661,7 +12867,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -12742,7 +12948,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Wholesale distribution</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -12823,7 +13029,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -12904,7 +13110,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -12985,7 +13191,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -13066,7 +13272,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Dental practices</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -13147,7 +13353,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Dental practices</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -13228,7 +13434,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -13309,7 +13515,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -13390,7 +13596,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -13471,7 +13677,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -13552,7 +13758,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -13633,7 +13839,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Real Estate Management &amp; Development</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -13709,12 +13915,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -13795,7 +14001,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -13876,7 +14082,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -13957,7 +14163,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Furniture &amp; interiors</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -14038,7 +14244,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Dental practices</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -14114,12 +14320,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Life Sciences</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -14200,7 +14406,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>GP &amp; primary care practices</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -14281,7 +14487,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>GP &amp; primary care practices</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -14362,7 +14568,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -14443,7 +14649,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -14519,12 +14725,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Media &amp; Creative</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -14605,7 +14811,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Mortgage broking &amp; financial advisory</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -14681,12 +14887,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Transport &amp; Logistics</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -14762,12 +14968,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Landscaping / Grounds Services</t>
+          <t>Construction &amp; Built Environment</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Landscaping &amp; grounds maintenance</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -14848,7 +15054,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Wholesale distribution</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -14929,7 +15135,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Farm machinery &amp; agri services</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -15010,7 +15216,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Real Estate Management &amp; Development</t>
+          <t>Wholesale distribution</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -15091,7 +15297,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -15172,7 +15378,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Furniture &amp; interiors</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -15253,7 +15459,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Solicitors &amp; legal practices</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -15334,7 +15540,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -15410,12 +15616,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Life Sciences</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -15496,7 +15702,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -15577,7 +15783,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Dental practices</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -15653,12 +15859,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -15739,7 +15945,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -15820,7 +16026,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -15901,7 +16107,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Dental practices</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -15982,7 +16188,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Farm machinery &amp; agri services</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -16063,7 +16269,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Steel fabrication &amp; metalwork</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -16144,7 +16350,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Wholesale distribution</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -16220,12 +16426,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -16301,12 +16507,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Transport &amp; Logistics</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -16387,7 +16593,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -16468,7 +16674,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Roofing &amp; cladding</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -16549,7 +16755,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Roofing &amp; cladding</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -16625,12 +16831,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -16711,7 +16917,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -16787,12 +16993,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -16873,7 +17079,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Farm machinery &amp; agri services</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -16954,7 +17160,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Garden centres &amp; nurseries</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -17035,7 +17241,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -17116,7 +17322,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Wholesale distribution</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -17192,12 +17398,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Real Estate Management &amp; Development</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -17273,12 +17479,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -17359,7 +17565,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -17440,7 +17646,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Road haulage &amp; freight</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -17521,7 +17727,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Printing &amp; signage</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -17597,12 +17803,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Transport &amp; Logistics</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -17678,12 +17884,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Transport &amp; Logistics</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -17764,7 +17970,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Farm machinery &amp; agri services</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -17845,7 +18051,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Wholesale distribution</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -17926,7 +18132,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Wholesale distribution</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -18007,7 +18213,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Physiotherapy &amp; rehabilitation</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -18083,12 +18289,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -18169,7 +18375,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -18245,12 +18451,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -18331,7 +18537,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Wholesale distribution</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -18412,7 +18618,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -18493,7 +18699,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -18574,7 +18780,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Fit-out &amp; refurbishment</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -18650,12 +18856,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -18736,7 +18942,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Hardware &amp; DIY</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -18817,7 +19023,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Car wash &amp; valeting</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -18893,12 +19099,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -18974,12 +19180,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -19055,12 +19261,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -19136,12 +19342,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -19217,12 +19423,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -19298,12 +19504,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -19379,12 +19585,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -19465,7 +19671,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -19546,7 +19752,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Farm machinery &amp; agri services</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -19627,7 +19833,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Wholesale distribution</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -19708,7 +19914,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Hotels &amp; guesthouses</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -19789,7 +19995,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Farm machinery &amp; agri services</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -19870,7 +20076,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -19946,12 +20152,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t/>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -20032,7 +20238,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -20113,7 +20319,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -20194,7 +20400,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -20270,12 +20476,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Playschools</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -20356,7 +20562,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -20437,7 +20643,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -20518,7 +20724,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Farm machinery &amp; agri services</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -20599,7 +20805,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Butchers &amp; artisan food producers</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -20680,7 +20886,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -20756,12 +20962,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -20837,12 +21043,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -20923,7 +21129,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -20999,12 +21205,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -21085,7 +21291,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -21161,12 +21367,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -21247,7 +21453,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Accounting &amp; bookkeeping practices</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -21328,7 +21534,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -21409,7 +21615,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -21490,7 +21696,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -21571,7 +21777,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Event venues &amp; catering</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -21647,12 +21853,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -21733,7 +21939,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Security &amp; guarding services</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -21814,7 +22020,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -21895,7 +22101,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -21976,7 +22182,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -22052,12 +22258,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -22138,7 +22344,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -22219,7 +22425,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -22300,7 +22506,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -22381,7 +22587,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -22462,7 +22668,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -22538,12 +22744,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -22619,12 +22825,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Retail &amp; Consumer</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -22705,7 +22911,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -22786,7 +22992,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -22867,7 +23073,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -22948,7 +23154,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -23029,7 +23235,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -23110,7 +23316,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -23191,7 +23397,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -23272,7 +23478,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Tyre &amp; exhaust centres</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -23353,7 +23559,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Furniture &amp; interiors</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -23434,7 +23640,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Event venues &amp; catering</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -23515,7 +23721,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -23596,7 +23802,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -23677,7 +23883,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -23753,12 +23959,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -23834,12 +24040,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -23915,12 +24121,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -23996,12 +24202,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -24082,7 +24288,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Motor repair &amp; servicing garages</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -24163,7 +24369,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -24244,7 +24450,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -24325,7 +24531,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -24406,7 +24612,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -24487,7 +24693,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -24568,7 +24774,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -24644,12 +24850,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -24730,7 +24936,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -24811,7 +25017,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -24887,12 +25093,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -24968,12 +25174,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -25054,7 +25260,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -25135,7 +25341,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -25216,7 +25422,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -25297,7 +25503,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -25373,12 +25579,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -25454,12 +25660,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -25540,7 +25746,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -25621,7 +25827,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -25702,7 +25908,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -25783,7 +25989,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Hotels &amp; guesthouses</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -25864,7 +26070,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -25945,7 +26151,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -26026,7 +26232,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -26107,7 +26313,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Security &amp; guarding services</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -26188,7 +26394,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -26264,12 +26470,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -26350,7 +26556,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Tyre &amp; exhaust centres</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -26431,7 +26637,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -26512,7 +26718,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -26593,7 +26799,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -26674,7 +26880,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -26755,7 +26961,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -26831,12 +27037,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -26912,12 +27118,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -26998,7 +27204,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -27079,7 +27285,7 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -27160,7 +27366,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -27236,12 +27442,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -27322,7 +27528,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -27403,7 +27609,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -27484,7 +27690,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -27565,7 +27771,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -27646,7 +27852,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -27727,7 +27933,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -27803,12 +28009,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -27889,7 +28095,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -27970,7 +28176,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Hotels &amp; guesthouses</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -28051,7 +28257,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -28132,7 +28338,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>PR &amp; marketing agencies</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -28213,7 +28419,7 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -28294,7 +28500,7 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -28370,12 +28576,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -28456,7 +28662,7 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -28537,7 +28743,7 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -28618,7 +28824,7 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Real Estate Management &amp; Development</t>
+          <t>Hotels &amp; guesthouses</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -28699,7 +28905,7 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -28775,12 +28981,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t/>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -28861,7 +29067,7 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -28942,7 +29148,7 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Media &amp; Entertainment</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -29023,7 +29229,7 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -29099,12 +29305,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -29180,12 +29386,12 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -29266,7 +29472,7 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Security &amp; guarding services</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -29342,12 +29548,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -29428,7 +29634,7 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -29509,7 +29715,7 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -29590,7 +29796,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -29671,7 +29877,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -29713,66 +29919,66 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A. O'TOOLE (CONFECTIONERS) LIMITED</t>
+          <t>Successful Pizza Business In North Dublin</t>
         </is>
       </c>
       <c r="B242">
-        <v>24.4</v>
+        <v>19.9</v>
       </c>
       <c r="C242">
-        <v>24.4</v>
+        <v>41.9</v>
       </c>
       <c r="D242">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
@@ -29787,33 +29993,33 @@
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>ic_packs/cro-72100/watch_note.md</t>
+          <t>ic_packs/name-county-successful-pizza-business-in-north-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Bonordic in Dublin</t>
+          <t>The Cappuccino Bar</t>
         </is>
       </c>
       <c r="B243">
-        <v>23.6</v>
+        <v>19.9</v>
       </c>
       <c r="C243">
-        <v>23.6</v>
+        <v>41.9</v>
       </c>
       <c r="D243">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -29828,12 +30034,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Retail &amp; Consumer</t>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Bars &amp; pubs</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -29843,12 +30049,12 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -29868,33 +30074,33 @@
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-bonordic-in-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-cappuccino-bar-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Brian Tracy Solutions Leadership &amp; Sales Training Consultancy in Galway</t>
+          <t>Coworking Master License Opportunity In Ireland</t>
         </is>
       </c>
       <c r="B244">
-        <v>23.6</v>
+        <v>19.3</v>
       </c>
       <c r="C244">
-        <v>23.6</v>
+        <v>41.3</v>
       </c>
       <c r="D244">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -29904,7 +30110,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -29914,7 +30120,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -29949,43 +30155,43 @@
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-brian-tracy-solutions-leadership-sales-training-consultancy-in-galway-galway/watch_note.md</t>
+          <t>ic_packs/name-county-coworking-master-license-opportunity-in-ireland-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Brian Tracy Solutions Leadership &amp; Sales Training Consultancy in Swords</t>
+          <t>5SRE 5 STAR REAL ESTATE LIMITED</t>
         </is>
       </c>
       <c r="B245">
-        <v>23.6</v>
+        <v>18.4</v>
       </c>
       <c r="C245">
-        <v>23.6</v>
+        <v>40.4</v>
       </c>
       <c r="D245">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -29995,27 +30201,27 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
@@ -30030,43 +30236,43 @@
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-brian-tracy-solutions-leadership-sales-training-consultancy-in-swords-dublin/watch_note.md</t>
+          <t>ic_packs/cro-718110/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Energie fitness in Dublin</t>
+          <t>9TH IMPACT LIMITED</t>
         </is>
       </c>
       <c r="B246">
-        <v>23.6</v>
+        <v>18.4</v>
       </c>
       <c r="C246">
-        <v>23.6</v>
+        <v>40.4</v>
       </c>
       <c r="D246">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -30076,27 +30282,27 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O246" t="inlineStr">
@@ -30111,33 +30317,33 @@
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-energie-fitness-in-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/cro-552335/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Energie fitness in Swords</t>
+          <t>Bonordic in Galway</t>
         </is>
       </c>
       <c r="B247">
-        <v>23.6</v>
+        <v>18.4</v>
       </c>
       <c r="C247">
-        <v>23.6</v>
+        <v>40.4</v>
       </c>
       <c r="D247">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -30147,7 +30353,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -30157,7 +30363,7 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -30192,33 +30398,33 @@
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-energie-fitness-in-swords-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-bonordic-in-galway-galway/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Young Engineers Franchise in Dublin</t>
+          <t>Greenfeet Lawn Care Franchise in South Dublin</t>
         </is>
       </c>
       <c r="B248">
-        <v>23.6</v>
+        <v>17.7</v>
       </c>
       <c r="C248">
-        <v>23.6</v>
+        <v>39.7</v>
       </c>
       <c r="D248">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -30238,7 +30444,7 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -30273,73 +30479,73 @@
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-young-engineers-franchise-in-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-greenfeet-lawn-care-franchise-in-south-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>(POLYCRAFTS IRELAND LIMITED) OLL CHEARD EIRE TEORANTA</t>
+          <t>Activewear Brand Online Business</t>
         </is>
       </c>
       <c r="B249">
-        <v>23.1</v>
+        <v>17.3</v>
       </c>
       <c r="C249">
-        <v>23.1</v>
+        <v>39.3</v>
       </c>
       <c r="D249">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
@@ -30354,38 +30560,38 @@
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>ic_packs/cro-106973/watch_note.md</t>
+          <t>ic_packs/name-county-activewear-brand-online-business-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2TYPE3 SUSTAINABILITY PARTNERS LIMITED</t>
+          <t>Established Pizzeria Killarney</t>
         </is>
       </c>
       <c r="B250">
-        <v>23.1</v>
+        <v>17.3</v>
       </c>
       <c r="C250">
-        <v>23.1</v>
+        <v>39.3</v>
       </c>
       <c r="D250">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -30395,32 +30601,32 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t/>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O250" t="inlineStr">
@@ -30435,73 +30641,73 @@
       </c>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>ic_packs/cro-462330/watch_note.md</t>
+          <t>ic_packs/name-county-established-pizzeria-killarney-galway/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>36 O'CONNELL STREET MANAGEMENT LIMITED</t>
+          <t>Established Tyre Shop/Service Business</t>
         </is>
       </c>
       <c r="B251">
-        <v>23.1</v>
+        <v>17.3</v>
       </c>
       <c r="C251">
-        <v>23.1</v>
+        <v>39.3</v>
       </c>
       <c r="D251">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t/>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Tyre &amp; exhaust centres</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O251" t="inlineStr">
@@ -30516,73 +30722,73 @@
       </c>
       <c r="Q251" t="inlineStr">
         <is>
-          <t>ic_packs/cro-360393/watch_note.md</t>
+          <t>ic_packs/name-county-established-tyre-shop-service-business-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>3D VENTURES LIMITED</t>
+          <t>Turnkey Hair Salon For Sale in Dublin 24</t>
         </is>
       </c>
       <c r="B252">
-        <v>23.1</v>
+        <v>17.3</v>
       </c>
       <c r="C252">
-        <v>23.1</v>
+        <v>39.3</v>
       </c>
       <c r="D252">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t/>
+          <t>Retail &amp; Consumer</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Specialist retail (sports, outdoors, music)</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O252" t="inlineStr">
@@ -30597,73 +30803,73 @@
       </c>
       <c r="Q252" t="inlineStr">
         <is>
-          <t>ic_packs/cro-470032/watch_note.md</t>
+          <t>ic_packs/name-county-turnkey-hair-salon-for-sale-in-dublin-24-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A &amp; M. DISTRIBUTORS LIMITED</t>
+          <t>Commercial Kitchen And Food Production Facility</t>
         </is>
       </c>
       <c r="B253">
-        <v>23.1</v>
+        <v>16.6</v>
       </c>
       <c r="C253">
-        <v>23.1</v>
+        <v>38.6</v>
       </c>
       <c r="D253">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O253" t="inlineStr">
@@ -30678,73 +30884,73 @@
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>ic_packs/cro-226593/watch_note.md</t>
+          <t>ic_packs/name-county-commercial-kitchen-and-food-production-facility-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A &amp; P AVIATION LIMITED</t>
+          <t>E-commerce Store l €1200PM Profits</t>
         </is>
       </c>
       <c r="B254">
-        <v>23.1</v>
+        <v>16.6</v>
       </c>
       <c r="C254">
-        <v>23.1</v>
+        <v>38.6</v>
       </c>
       <c r="D254">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
@@ -30759,73 +30965,73 @@
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>ic_packs/cro-189250/watch_note.md</t>
+          <t>ic_packs/name-county-e-commerce-store-l-1200pm-profits-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A. B. C. CUISINES LIMITED</t>
+          <t>Exceptional Restaurant, Takeaway</t>
         </is>
       </c>
       <c r="B255">
-        <v>23.1</v>
+        <v>16.6</v>
       </c>
       <c r="C255">
-        <v>23.1</v>
+        <v>38.6</v>
       </c>
       <c r="D255">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t/>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
@@ -30840,38 +31046,38 @@
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>ic_packs/cro-58944/watch_note.md</t>
+          <t>ic_packs/name-county-exceptional-restaurant-takeaway-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A. G. FEED LIMITED</t>
+          <t>Woodford Garden Centre</t>
         </is>
       </c>
       <c r="B256">
-        <v>23.1</v>
+        <v>16.6</v>
       </c>
       <c r="C256">
-        <v>23.1</v>
+        <v>38.6</v>
       </c>
       <c r="D256">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -30881,32 +31087,32 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t/>
+          <t>Retail &amp; Consumer</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Garden centres &amp; nurseries</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
@@ -30921,73 +31127,73 @@
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>ic_packs/cro-347425/watch_note.md</t>
+          <t>ic_packs/name-county-woodford-garden-centre-galway/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A. K. D. LIMITED</t>
+          <t>GPS Device Franchise Opportunity</t>
         </is>
       </c>
       <c r="B257">
-        <v>23.1</v>
+        <v>15.8</v>
       </c>
       <c r="C257">
-        <v>23.1</v>
+        <v>37.8</v>
       </c>
       <c r="D257">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
@@ -31002,33 +31208,33 @@
       </c>
       <c r="Q257" t="inlineStr">
         <is>
-          <t>ic_packs/cro-75533/watch_note.md</t>
+          <t>ic_packs/name-county-gps-device-franchise-opportunity-ireland/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A. LOOK LIMITED</t>
+          <t>A &amp; S ROOFING &amp; FLOORING LIMITED</t>
         </is>
       </c>
       <c r="B258">
-        <v>23.1</v>
+        <v>15.0</v>
       </c>
       <c r="C258">
-        <v>23.1</v>
+        <v>37.0</v>
       </c>
       <c r="D258">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -31043,12 +31249,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t/>
+          <t>Construction &amp; Built Environment</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Roofing &amp; cladding</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -31068,7 +31274,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
@@ -31083,33 +31289,33 @@
       </c>
       <c r="Q258" t="inlineStr">
         <is>
-          <t>ic_packs/cro-322344/watch_note.md</t>
+          <t>ic_packs/cro-89969/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A.1. DEV CHIMNEY CO. LIMITED</t>
+          <t>A B P MANUFACTURING MACHINERY LIMITED</t>
         </is>
       </c>
       <c r="B259">
-        <v>23.1</v>
+        <v>15.0</v>
       </c>
       <c r="C259">
-        <v>23.1</v>
+        <v>37.0</v>
       </c>
       <c r="D259">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -31124,12 +31330,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t/>
+          <t>Industrials &amp; Engineering</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -31149,7 +31355,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
@@ -31164,33 +31370,33 @@
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t>ic_packs/cro-346214/watch_note.md</t>
+          <t>ic_packs/cro-463722/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A.B.V.G. (A BRIGHTER VISION GENERALLY) LIMITED</t>
+          <t>A.1. BUILDERS LIMITED</t>
         </is>
       </c>
       <c r="B260">
-        <v>23.1</v>
+        <v>15.0</v>
       </c>
       <c r="C260">
-        <v>23.1</v>
+        <v>37.0</v>
       </c>
       <c r="D260">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -31205,12 +31411,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t/>
+          <t>Construction &amp; Built Environment</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Civil &amp; groundworks</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -31230,7 +31436,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
@@ -31245,73 +31451,73 @@
       </c>
       <c r="Q260" t="inlineStr">
         <is>
-          <t>ic_packs/cro-465159/watch_note.md</t>
+          <t>ic_packs/cro-129924/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A.E.R. LIMITED</t>
+          <t>Filling Stations</t>
         </is>
       </c>
       <c r="B261">
-        <v>23.1</v>
+        <v>13.9</v>
       </c>
       <c r="C261">
-        <v>23.1</v>
+        <v>35.9</v>
       </c>
       <c r="D261">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
@@ -31326,73 +31532,73 @@
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t>ic_packs/cro-240545/watch_note.md</t>
+          <t>ic_packs/name-county-filling-stations-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A.M. &amp; D. LIMITED</t>
+          <t>Profitable And High Potential Natural Juices Business Ireland</t>
         </is>
       </c>
       <c r="B262">
-        <v>23.1</v>
+        <v>13.9</v>
       </c>
       <c r="C262">
-        <v>23.1</v>
+        <v>35.9</v>
       </c>
       <c r="D262">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
@@ -31407,33 +31613,33 @@
       </c>
       <c r="Q262" t="inlineStr">
         <is>
-          <t>ic_packs/cro-214417/watch_note.md</t>
+          <t>ic_packs/name-county-profitable-and-high-potential-natural-juices-business-ireland-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A.M.T. GALWAY LIMITED</t>
+          <t>A.P. MCCARTHY PLANNING CONSULTANTS LIMITED</t>
         </is>
       </c>
       <c r="B263">
-        <v>23.1</v>
+        <v>13.7</v>
       </c>
       <c r="C263">
-        <v>23.1</v>
+        <v>35.7</v>
       </c>
       <c r="D263">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -31448,12 +31654,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -31473,7 +31679,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
@@ -31488,33 +31694,33 @@
       </c>
       <c r="Q263" t="inlineStr">
         <is>
-          <t>ic_packs/cro-162537/watch_note.md</t>
+          <t>ic_packs/cro-328511/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>GARDEN LEISURE PRODUCTS LIMITED/TROSCAN GHAIRDINI TEORANTA</t>
+          <t>A. M. S. ENGINEERING COMPANY LIMITED</t>
         </is>
       </c>
       <c r="B264">
-        <v>23.1</v>
+        <v>12.3</v>
       </c>
       <c r="C264">
-        <v>23.1</v>
+        <v>34.3</v>
       </c>
       <c r="D264">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -31529,12 +31735,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t/>
+          <t>Industrials &amp; Engineering</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Precision engineering &amp; manufacturing</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -31554,7 +31760,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
@@ -31569,73 +31775,73 @@
       </c>
       <c r="Q264" t="inlineStr">
         <is>
-          <t>ic_packs/cro-157217/watch_note.md</t>
+          <t>ic_packs/cro-28525/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>GARDEN PRIDE TOOL HIRE LIMITED</t>
+          <t>Surveillance Device Sales Partner Opportunity</t>
         </is>
       </c>
       <c r="B265">
-        <v>23.1</v>
+        <v>11.6</v>
       </c>
       <c r="C265">
-        <v>23.1</v>
+        <v>33.6</v>
       </c>
       <c r="D265">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t/>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
@@ -31650,33 +31856,33 @@
       </c>
       <c r="Q265" t="inlineStr">
         <is>
-          <t>ic_packs/cro-369982/watch_note.md</t>
+          <t>ic_packs/name-county-surveillance-device-sales-partner-opportunity-ireland/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>LAWN RANGER LIMITED</t>
+          <t>A &amp; D; ADVERTISING AND DESIGN CONSULTANTS LIMITED</t>
         </is>
       </c>
       <c r="B266">
-        <v>23.1</v>
+        <v>11.0</v>
       </c>
       <c r="C266">
-        <v>23.1</v>
+        <v>33.0</v>
       </c>
       <c r="D266">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -31691,12 +31897,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -31716,7 +31922,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
@@ -31731,33 +31937,33 @@
       </c>
       <c r="Q266" t="inlineStr">
         <is>
-          <t>ic_packs/cro-345282/watch_note.md</t>
+          <t>ic_packs/cro-234849/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>40 DEGREES LIMITED</t>
+          <t>A LEONARD MANAGEMENT &amp; CONSULTING LIMITED</t>
         </is>
       </c>
       <c r="B267">
-        <v>21.0</v>
+        <v>11.0</v>
       </c>
       <c r="C267">
-        <v>21.0</v>
+        <v>33.0</v>
       </c>
       <c r="D267">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -31772,12 +31978,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -31797,7 +32003,7 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
@@ -31812,33 +32018,33 @@
       </c>
       <c r="Q267" t="inlineStr">
         <is>
-          <t>ic_packs/cro-270945/watch_note.md</t>
+          <t>ic_packs/cro-481667/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>4D SOFTWARE LIMITED</t>
+          <t>GROUNDSOURCE LIMITED</t>
         </is>
       </c>
       <c r="B268">
-        <v>21.0</v>
+        <v>10.1</v>
       </c>
       <c r="C268">
-        <v>21.0</v>
+        <v>32.1</v>
       </c>
       <c r="D268">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -31853,12 +32059,12 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -31878,7 +32084,7 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
@@ -31893,73 +32099,73 @@
       </c>
       <c r="Q268" t="inlineStr">
         <is>
-          <t>ic_packs/cro-406809/watch_note.md</t>
+          <t>ic_packs/cro-385921/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A J D DEVELOPMENTS LIMITED</t>
+          <t>KD ECO+ Laminates - Services Franchise in Dublin</t>
         </is>
       </c>
       <c r="B269">
-        <v>21.0</v>
+        <v>9.7</v>
       </c>
       <c r="C269">
-        <v>21.0</v>
+        <v>31.7</v>
       </c>
       <c r="D269">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
@@ -31974,38 +32180,38 @@
       </c>
       <c r="Q269" t="inlineStr">
         <is>
-          <t>ic_packs/cro-328171/watch_note.md</t>
+          <t>ic_packs/name-county-kd-eco-laminates-services-franchise-in-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A.M. &amp; D. HOLDINGS LIMITED</t>
+          <t>KD ECO+ Laminates - Services Franchise in Galway</t>
         </is>
       </c>
       <c r="B270">
-        <v>21.0</v>
+        <v>9.7</v>
       </c>
       <c r="C270">
-        <v>21.0</v>
+        <v>31.7</v>
       </c>
       <c r="D270">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>discard</t>
+          <t>watchlist_only</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Outside scope or too weak for the current origination workflow.</t>
+          <t>Keep visible but do not spend major time until better evidence appears.</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -32015,32 +32221,32 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O270" t="inlineStr">
@@ -32055,21 +32261,21 @@
       </c>
       <c r="Q270" t="inlineStr">
         <is>
-          <t>ic_packs/cro-217915/watch_note.md</t>
+          <t>ic_packs/name-county-kd-eco-laminates-services-franchise-in-galway-galway/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Successful Pizza Business In North Dublin</t>
+          <t>A.E.D. SECURITY INSTALLATIONS LIMITED</t>
         </is>
       </c>
       <c r="B271">
-        <v>19.9</v>
+        <v>8.4</v>
       </c>
       <c r="C271">
-        <v>41.9</v>
+        <v>30.4</v>
       </c>
       <c r="D271">
         <v>22.0</v>
@@ -32086,12 +32292,12 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -32101,22 +32307,22 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -32136,21 +32342,21 @@
       </c>
       <c r="Q271" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-successful-pizza-business-in-north-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/cro-359827/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>The Cappuccino Bar</t>
+          <t>High End Pizza Franchise - Only €5,000</t>
         </is>
       </c>
       <c r="B272">
-        <v>19.9</v>
+        <v>7.6</v>
       </c>
       <c r="C272">
-        <v>41.9</v>
+        <v>29.6</v>
       </c>
       <c r="D272">
         <v>22.0</v>
@@ -32177,12 +32383,12 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -32217,21 +32423,21 @@
       </c>
       <c r="Q272" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-cappuccino-bar-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-high-end-pizza-franchise-only-5-000-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Coworking Master License Opportunity In Ireland</t>
+          <t>Gym Franchise Opportunity</t>
         </is>
       </c>
       <c r="B273">
-        <v>19.3</v>
+        <v>7.2</v>
       </c>
       <c r="C273">
-        <v>41.3</v>
+        <v>29.2</v>
       </c>
       <c r="D273">
         <v>22.0</v>
@@ -32253,7 +32459,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -32263,7 +32469,7 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -32273,12 +32479,12 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -32298,21 +32504,21 @@
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-coworking-master-license-opportunity-in-ireland-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-gym-franchise-opportunity-ireland/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>5SRE 5 STAR REAL ESTATE LIMITED</t>
+          <t>Best.Energy - Energy Monitoring Franchise in Dublin</t>
         </is>
       </c>
       <c r="B274">
-        <v>18.4</v>
+        <v>7.0</v>
       </c>
       <c r="C274">
-        <v>40.4</v>
+        <v>29.0</v>
       </c>
       <c r="D274">
         <v>22.0</v>
@@ -32329,42 +32535,42 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
@@ -32379,21 +32585,21 @@
       </c>
       <c r="Q274" t="inlineStr">
         <is>
-          <t>ic_packs/cro-718110/watch_note.md</t>
+          <t>ic_packs/name-county-best-energy-energy-monitoring-franchise-in-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>9TH IMPACT LIMITED</t>
+          <t>Franchise Pizzeria Restaurant l 3 Bed Apartment Galway</t>
         </is>
       </c>
       <c r="B275">
-        <v>18.4</v>
+        <v>6.7</v>
       </c>
       <c r="C275">
-        <v>40.4</v>
+        <v>28.7</v>
       </c>
       <c r="D275">
         <v>22.0</v>
@@ -32410,7 +32616,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -32420,32 +32626,32 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t/>
+          <t>Hospitality &amp; Tourism</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Restaurants &amp; cafes</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O275" t="inlineStr">
@@ -32460,21 +32666,21 @@
       </c>
       <c r="Q275" t="inlineStr">
         <is>
-          <t>ic_packs/cro-552335/watch_note.md</t>
+          <t>ic_packs/name-county-franchise-pizzeria-restaurant-l-3-bed-apartment-galway-galway/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Bonordic in Galway</t>
+          <t>(NEW AGE OFFICE FURNITURE LIMITED) TROSCAN OIFIGE NA H'AOISE NUA TEORANTA</t>
         </is>
       </c>
       <c r="B276">
-        <v>18.4</v>
+        <v>6.4</v>
       </c>
       <c r="C276">
-        <v>40.4</v>
+        <v>28.4</v>
       </c>
       <c r="D276">
         <v>22.0</v>
@@ -32491,7 +32697,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -32506,27 +32712,27 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Furniture &amp; interiors</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
@@ -32541,21 +32747,21 @@
       </c>
       <c r="Q276" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-bonordic-in-galway-galway/watch_note.md</t>
+          <t>ic_packs/cro-154946/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Greenfeet Lawn Care Franchise in South Dublin</t>
+          <t>Multi-Site Fitness Franchise Portfolio – Ireland</t>
         </is>
       </c>
       <c r="B277">
-        <v>17.7</v>
+        <v>5.0</v>
       </c>
       <c r="C277">
-        <v>39.7</v>
+        <v>27.0</v>
       </c>
       <c r="D277">
         <v>22.0</v>
@@ -32582,12 +32788,12 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Business Services</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -32622,21 +32828,21 @@
       </c>
       <c r="Q277" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-greenfeet-lawn-care-franchise-in-south-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-multi-site-fitness-franchise-portfolio-ireland-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Activewear Brand Online Business</t>
+          <t>Evoglide Automotive Franchise in Dublin</t>
         </is>
       </c>
       <c r="B278">
-        <v>17.3</v>
+        <v>4.3</v>
       </c>
       <c r="C278">
-        <v>39.3</v>
+        <v>26.3</v>
       </c>
       <c r="D278">
         <v>22.0</v>
@@ -32668,7 +32874,7 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -32703,21 +32909,21 @@
       </c>
       <c r="Q278" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-activewear-brand-online-business-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-evoglide-automotive-franchise-in-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Established Pizzeria Killarney</t>
+          <t>Four Star Pizza in Balbriggan</t>
         </is>
       </c>
       <c r="B279">
-        <v>17.3</v>
+        <v>4.3</v>
       </c>
       <c r="C279">
-        <v>39.3</v>
+        <v>26.3</v>
       </c>
       <c r="D279">
         <v>22.0</v>
@@ -32739,17 +32945,17 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -32784,21 +32990,21 @@
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-established-pizzeria-killarney-galway/watch_note.md</t>
+          <t>ic_packs/name-county-four-star-pizza-in-balbriggan-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Established Tyre Shop/Service Business</t>
+          <t>Gecko Hospitality Recruitment Franchise in Dublin</t>
         </is>
       </c>
       <c r="B280">
-        <v>17.3</v>
+        <v>4.3</v>
       </c>
       <c r="C280">
-        <v>39.3</v>
+        <v>26.3</v>
       </c>
       <c r="D280">
         <v>22.0</v>
@@ -32825,12 +33031,12 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Recruitment &amp; staffing agencies</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -32865,21 +33071,21 @@
       </c>
       <c r="Q280" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-established-tyre-shop-service-business-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-gecko-hospitality-recruitment-franchise-in-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Turnkey Hair Salon For Sale in Dublin 24</t>
+          <t>Signarama International Master Franchise Opportunities</t>
         </is>
       </c>
       <c r="B281">
-        <v>17.3</v>
+        <v>4.3</v>
       </c>
       <c r="C281">
-        <v>39.3</v>
+        <v>26.3</v>
       </c>
       <c r="D281">
         <v>22.0</v>
@@ -32906,12 +33112,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>Retail &amp; Consumer</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -32946,21 +33152,21 @@
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-turnkey-hair-salon-for-sale-in-dublin-24-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-signarama-international-master-franchise-opportunities-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Commercial Kitchen And Food Production Facility</t>
+          <t>Specialist Glass Repairs - Glass &amp; Acrylic Repair Franchise in Dublin</t>
         </is>
       </c>
       <c r="B282">
-        <v>16.6</v>
+        <v>4.3</v>
       </c>
       <c r="C282">
-        <v>38.6</v>
+        <v>26.3</v>
       </c>
       <c r="D282">
         <v>22.0</v>
@@ -32992,7 +33198,7 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -33027,21 +33233,21 @@
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-commercial-kitchen-and-food-production-facility-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-specialist-glass-repairs-glass-acrylic-repair-franchise-in-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>E-commerce Store l €1200PM Profits</t>
+          <t>WeddingBox Event Planning Franchise in Dublin</t>
         </is>
       </c>
       <c r="B283">
-        <v>16.6</v>
+        <v>4.3</v>
       </c>
       <c r="C283">
-        <v>38.6</v>
+        <v>26.3</v>
       </c>
       <c r="D283">
         <v>22.0</v>
@@ -33068,12 +33274,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Retail &amp; Consumer</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -33108,21 +33314,21 @@
       </c>
       <c r="Q283" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-e-commerce-store-l-1200pm-profits-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-weddingbox-event-planning-franchise-in-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Exceptional Restaurant, Takeaway</t>
+          <t>GARDEN GREEN ENERGY LIMITED</t>
         </is>
       </c>
       <c r="B284">
-        <v>16.6</v>
+        <v>3.8</v>
       </c>
       <c r="C284">
-        <v>38.6</v>
+        <v>25.8</v>
       </c>
       <c r="D284">
         <v>22.0</v>
@@ -33139,42 +33345,42 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O284" t="inlineStr">
@@ -33189,38 +33395,38 @@
       </c>
       <c r="Q284" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-exceptional-restaurant-takeaway-dublin/watch_note.md</t>
+          <t>ic_packs/cro-463334/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Woodford Garden Centre</t>
+          <t>(POLYCRAFTS IRELAND LIMITED) OLL CHEARD EIRE TEORANTA</t>
         </is>
       </c>
       <c r="B285">
-        <v>16.6</v>
+        <v>0.0</v>
       </c>
       <c r="C285">
-        <v>38.6</v>
+        <v>23.1</v>
       </c>
       <c r="D285">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -33230,32 +33436,32 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>Retail &amp; Consumer</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>Real Estate Management &amp; Development</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O285" t="inlineStr">
@@ -33270,73 +33476,73 @@
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-woodford-garden-centre-galway/watch_note.md</t>
+          <t>ic_packs/cro-106973/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>GPS Device Franchise Opportunity</t>
+          <t>2TYPE3 SUSTAINABILITY PARTNERS LIMITED</t>
         </is>
       </c>
       <c r="B286">
-        <v>15.8</v>
+        <v>0.0</v>
       </c>
       <c r="C286">
-        <v>37.8</v>
+        <v>23.1</v>
       </c>
       <c r="D286">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>Transport &amp; Logistics</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O286" t="inlineStr">
@@ -33351,33 +33557,33 @@
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-gps-device-franchise-opportunity-ireland/watch_note.md</t>
+          <t>ic_packs/cro-462330/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>A &amp; S ROOFING &amp; FLOORING LIMITED</t>
+          <t>36 O'CONNELL STREET MANAGEMENT LIMITED</t>
         </is>
       </c>
       <c r="B287">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="C287">
-        <v>37.0</v>
+        <v>23.1</v>
       </c>
       <c r="D287">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -33392,12 +33598,12 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>Construction Services</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
@@ -33417,7 +33623,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O287" t="inlineStr">
@@ -33432,33 +33638,33 @@
       </c>
       <c r="Q287" t="inlineStr">
         <is>
-          <t>ic_packs/cro-89969/watch_note.md</t>
+          <t>ic_packs/cro-360393/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>A B P MANUFACTURING MACHINERY LIMITED</t>
+          <t>3D VENTURES LIMITED</t>
         </is>
       </c>
       <c r="B288">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="C288">
-        <v>37.0</v>
+        <v>23.1</v>
       </c>
       <c r="D288">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -33473,12 +33679,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -33498,7 +33704,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O288" t="inlineStr">
@@ -33513,33 +33719,33 @@
       </c>
       <c r="Q288" t="inlineStr">
         <is>
-          <t>ic_packs/cro-463722/watch_note.md</t>
+          <t>ic_packs/cro-470032/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>A.1. BUILDERS LIMITED</t>
+          <t>40 DEGREES LIMITED</t>
         </is>
       </c>
       <c r="B289">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="C289">
-        <v>37.0</v>
+        <v>21.0</v>
       </c>
       <c r="D289">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -33554,12 +33760,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Construction Services</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -33579,7 +33785,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O289" t="inlineStr">
@@ -33594,73 +33800,73 @@
       </c>
       <c r="Q289" t="inlineStr">
         <is>
-          <t>ic_packs/cro-129924/watch_note.md</t>
+          <t>ic_packs/cro-270945/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Filling Stations</t>
+          <t>4D SOFTWARE LIMITED</t>
         </is>
       </c>
       <c r="B290">
-        <v>13.9</v>
+        <v>0.0</v>
       </c>
       <c r="C290">
-        <v>35.9</v>
+        <v>21.0</v>
       </c>
       <c r="D290">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>Retail &amp; Consumer</t>
+          <t>Technology &amp; IT Services</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Software development</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
@@ -33675,43 +33881,43 @@
       </c>
       <c r="Q290" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-filling-stations-dublin/watch_note.md</t>
+          <t>ic_packs/cro-406809/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Profitable And High Potential Natural Juices Business Ireland</t>
+          <t>A &amp; M. DISTRIBUTORS LIMITED</t>
         </is>
       </c>
       <c r="B291">
-        <v>13.9</v>
+        <v>0.0</v>
       </c>
       <c r="C291">
-        <v>35.9</v>
+        <v>23.1</v>
       </c>
       <c r="D291">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -33721,27 +33927,27 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O291" t="inlineStr">
@@ -33756,33 +33962,33 @@
       </c>
       <c r="Q291" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-profitable-and-high-potential-natural-juices-business-ireland-dublin/watch_note.md</t>
+          <t>ic_packs/cro-226593/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>A.P. MCCARTHY PLANNING CONSULTANTS LIMITED</t>
+          <t>A &amp; P AVIATION LIMITED</t>
         </is>
       </c>
       <c r="B292">
-        <v>13.7</v>
+        <v>0.0</v>
       </c>
       <c r="C292">
-        <v>35.7</v>
+        <v>23.1</v>
       </c>
       <c r="D292">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -33797,12 +34003,12 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -33822,7 +34028,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O292" t="inlineStr">
@@ -33837,33 +34043,33 @@
       </c>
       <c r="Q292" t="inlineStr">
         <is>
-          <t>ic_packs/cro-328511/watch_note.md</t>
+          <t>ic_packs/cro-189250/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>A. M. S. ENGINEERING COMPANY LIMITED</t>
+          <t>A J D DEVELOPMENTS LIMITED</t>
         </is>
       </c>
       <c r="B293">
-        <v>12.3</v>
+        <v>0.0</v>
       </c>
       <c r="C293">
-        <v>34.3</v>
+        <v>21.0</v>
       </c>
       <c r="D293">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -33878,12 +34084,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -33903,7 +34109,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
@@ -33918,73 +34124,73 @@
       </c>
       <c r="Q293" t="inlineStr">
         <is>
-          <t>ic_packs/cro-28525/watch_note.md</t>
+          <t>ic_packs/cro-328171/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Surveillance Device Sales Partner Opportunity</t>
+          <t>A. B. C. CUISINES LIMITED</t>
         </is>
       </c>
       <c r="B294">
-        <v>11.6</v>
+        <v>0.0</v>
       </c>
       <c r="C294">
-        <v>33.6</v>
+        <v>23.1</v>
       </c>
       <c r="D294">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
@@ -33999,33 +34205,33 @@
       </c>
       <c r="Q294" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-surveillance-device-sales-partner-opportunity-ireland/watch_note.md</t>
+          <t>ic_packs/cro-58944/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>A &amp; D; ADVERTISING AND DESIGN CONSULTANTS LIMITED</t>
+          <t>A. G. FEED LIMITED</t>
         </is>
       </c>
       <c r="B295">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="C295">
-        <v>33.0</v>
+        <v>23.1</v>
       </c>
       <c r="D295">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -34040,12 +34246,12 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -34065,7 +34271,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
@@ -34080,33 +34286,33 @@
       </c>
       <c r="Q295" t="inlineStr">
         <is>
-          <t>ic_packs/cro-234849/watch_note.md</t>
+          <t>ic_packs/cro-347425/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>A LEONARD MANAGEMENT &amp; CONSULTING LIMITED</t>
+          <t>A. K. D. LIMITED</t>
         </is>
       </c>
       <c r="B296">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="C296">
-        <v>33.0</v>
+        <v>23.1</v>
       </c>
       <c r="D296">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -34121,12 +34327,12 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -34146,7 +34352,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O296" t="inlineStr">
@@ -34161,33 +34367,33 @@
       </c>
       <c r="Q296" t="inlineStr">
         <is>
-          <t>ic_packs/cro-481667/watch_note.md</t>
+          <t>ic_packs/cro-75533/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>GROUNDSOURCE LIMITED</t>
+          <t>A. LOOK LIMITED</t>
         </is>
       </c>
       <c r="B297">
-        <v>10.1</v>
+        <v>0.0</v>
       </c>
       <c r="C297">
-        <v>32.1</v>
+        <v>23.1</v>
       </c>
       <c r="D297">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -34202,12 +34408,12 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
@@ -34227,7 +34433,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
@@ -34242,43 +34448,43 @@
       </c>
       <c r="Q297" t="inlineStr">
         <is>
-          <t>ic_packs/cro-385921/watch_note.md</t>
+          <t>ic_packs/cro-322344/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>KD ECO+ Laminates - Services Franchise in Dublin</t>
+          <t>A. O'TOOLE (CONFECTIONERS) LIMITED</t>
         </is>
       </c>
       <c r="B298">
-        <v>9.7</v>
+        <v>0.0</v>
       </c>
       <c r="C298">
-        <v>31.7</v>
+        <v>24.4</v>
       </c>
       <c r="D298">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -34288,27 +34494,27 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
@@ -34323,38 +34529,38 @@
       </c>
       <c r="Q298" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-kd-eco-laminates-services-franchise-in-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/cro-72100/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>KD ECO+ Laminates - Services Franchise in Galway</t>
+          <t>A.1. DEV CHIMNEY CO. LIMITED</t>
         </is>
       </c>
       <c r="B299">
-        <v>9.7</v>
+        <v>0.0</v>
       </c>
       <c r="C299">
-        <v>31.7</v>
+        <v>23.1</v>
       </c>
       <c r="D299">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -34369,27 +34575,27 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
@@ -34404,33 +34610,33 @@
       </c>
       <c r="Q299" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-kd-eco-laminates-services-franchise-in-galway-galway/watch_note.md</t>
+          <t>ic_packs/cro-346214/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>A.E.D. SECURITY INSTALLATIONS LIMITED</t>
+          <t>A.B.V.G. (A BRIGHTER VISION GENERALLY) LIMITED</t>
         </is>
       </c>
       <c r="B300">
-        <v>8.4</v>
+        <v>0.0</v>
       </c>
       <c r="C300">
-        <v>30.4</v>
+        <v>23.1</v>
       </c>
       <c r="D300">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -34445,12 +34651,12 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Facilities Services</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>Capital Goods &amp; Commercial Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -34470,7 +34676,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
@@ -34485,73 +34691,73 @@
       </c>
       <c r="Q300" t="inlineStr">
         <is>
-          <t>ic_packs/cro-359827/watch_note.md</t>
+          <t>ic_packs/cro-465159/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>High End Pizza Franchise - Only €5,000</t>
+          <t>A.E.R. LIMITED</t>
         </is>
       </c>
       <c r="B301">
-        <v>7.6</v>
+        <v>0.0</v>
       </c>
       <c r="C301">
-        <v>29.6</v>
+        <v>23.1</v>
       </c>
       <c r="D301">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O301" t="inlineStr">
@@ -34566,43 +34772,43 @@
       </c>
       <c r="Q301" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-high-end-pizza-franchise-only-5-000-dublin/watch_note.md</t>
+          <t>ic_packs/cro-240545/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Gym Franchise Opportunity</t>
+          <t>A.M. &amp; D. HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="B302">
-        <v>7.2</v>
+        <v>0.0</v>
       </c>
       <c r="C302">
-        <v>29.2</v>
+        <v>21.0</v>
       </c>
       <c r="D302">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -34612,27 +34818,27 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent and asking-price evidence.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O302" t="inlineStr">
@@ -34647,43 +34853,43 @@
       </c>
       <c r="Q302" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-gym-franchise-opportunity-ireland/watch_note.md</t>
+          <t>ic_packs/cro-217915/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Best.Energy - Energy Monitoring Franchise in Dublin</t>
+          <t>A.M. &amp; D. LIMITED</t>
         </is>
       </c>
       <c r="B303">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="C303">
-        <v>29.0</v>
+        <v>23.1</v>
       </c>
       <c r="D303">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -34693,27 +34899,27 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
@@ -34728,38 +34934,38 @@
       </c>
       <c r="Q303" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-best-energy-energy-monitoring-franchise-in-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/cro-214417/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Franchise Pizzeria Restaurant l 3 Bed Apartment Galway</t>
+          <t>A.M.T. GALWAY LIMITED</t>
         </is>
       </c>
       <c r="B304">
-        <v>6.7</v>
+        <v>0.0</v>
       </c>
       <c r="C304">
-        <v>28.7</v>
+        <v>23.1</v>
       </c>
       <c r="D304">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -34769,32 +34975,32 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism</t>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
@@ -34809,73 +35015,73 @@
       </c>
       <c r="Q304" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-franchise-pizzeria-restaurant-l-3-bed-apartment-galway-galway/watch_note.md</t>
+          <t>ic_packs/cro-162537/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>(NEW AGE OFFICE FURNITURE LIMITED) TROSCAN OIFIGE NA H'AOISE NUA TEORANTA</t>
+          <t>Bonordic in Dublin</t>
         </is>
       </c>
       <c r="B305">
-        <v>6.4</v>
+        <v>0.0</v>
       </c>
       <c r="C305">
-        <v>28.4</v>
+        <v>23.6</v>
       </c>
       <c r="D305">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
@@ -34890,33 +35096,33 @@
       </c>
       <c r="Q305" t="inlineStr">
         <is>
-          <t>ic_packs/cro-154946/watch_note.md</t>
+          <t>ic_packs/name-county-bonordic-in-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Multi-Site Fitness Franchise Portfolio – Ireland</t>
+          <t>Brian Tracy Solutions Leadership &amp; Sales Training Consultancy in Galway</t>
         </is>
       </c>
       <c r="B306">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="C306">
-        <v>27.0</v>
+        <v>23.6</v>
       </c>
       <c r="D306">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -34926,7 +35132,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -34936,7 +35142,7 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -34971,33 +35177,33 @@
       </c>
       <c r="Q306" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-multi-site-fitness-franchise-portfolio-ireland-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-brian-tracy-solutions-leadership-sales-training-consultancy-in-galway-galway/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Evoglide Automotive Franchise in Dublin</t>
+          <t>Brian Tracy Solutions Leadership &amp; Sales Training Consultancy in Swords</t>
         </is>
       </c>
       <c r="B307">
-        <v>4.3</v>
+        <v>0.0</v>
       </c>
       <c r="C307">
-        <v>26.3</v>
+        <v>23.6</v>
       </c>
       <c r="D307">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -35017,7 +35223,7 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -35052,33 +35258,33 @@
       </c>
       <c r="Q307" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-evoglide-automotive-franchise-in-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-brian-tracy-solutions-leadership-sales-training-consultancy-in-swords-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Four Star Pizza in Balbriggan</t>
+          <t>Energie fitness in Dublin</t>
         </is>
       </c>
       <c r="B308">
-        <v>4.3</v>
+        <v>0.0</v>
       </c>
       <c r="C308">
-        <v>26.3</v>
+        <v>23.6</v>
       </c>
       <c r="D308">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -35098,7 +35304,7 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -35133,33 +35339,33 @@
       </c>
       <c r="Q308" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-four-star-pizza-in-balbriggan-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-energie-fitness-in-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Gecko Hospitality Recruitment Franchise in Dublin</t>
+          <t>Energie fitness in Swords</t>
         </is>
       </c>
       <c r="B309">
-        <v>4.3</v>
+        <v>0.0</v>
       </c>
       <c r="C309">
-        <v>26.3</v>
+        <v>23.6</v>
       </c>
       <c r="D309">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -35179,7 +35385,7 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>Software &amp; Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -35214,43 +35420,43 @@
       </c>
       <c r="Q309" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-gecko-hospitality-recruitment-franchise-in-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/name-county-energie-fitness-in-swords-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Signarama International Master Franchise Opportunities</t>
+          <t>GARDEN LEISURE PRODUCTS LIMITED/TROSCAN GHAIRDINI TEORANTA</t>
         </is>
       </c>
       <c r="B310">
-        <v>4.3</v>
+        <v>0.0</v>
       </c>
       <c r="C310">
-        <v>26.3</v>
+        <v>23.1</v>
       </c>
       <c r="D310">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -35260,27 +35466,27 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
@@ -35295,43 +35501,43 @@
       </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-signarama-international-master-franchise-opportunities-dublin/watch_note.md</t>
+          <t>ic_packs/cro-157217/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Specialist Glass Repairs - Glass &amp; Acrylic Repair Franchise in Dublin</t>
+          <t>GARDEN PRIDE TOOL HIRE LIMITED</t>
         </is>
       </c>
       <c r="B311">
-        <v>4.3</v>
+        <v>0.0</v>
       </c>
       <c r="C311">
-        <v>26.3</v>
+        <v>23.1</v>
       </c>
       <c r="D311">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -35341,27 +35547,27 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O311" t="inlineStr">
@@ -35376,43 +35582,43 @@
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-specialist-glass-repairs-glass-acrylic-repair-franchise-in-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/cro-369982/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>WeddingBox Event Planning Franchise in Dublin</t>
+          <t>LAWN RANGER LIMITED</t>
         </is>
       </c>
       <c r="B312">
-        <v>4.3</v>
+        <v>0.0</v>
       </c>
       <c r="C312">
-        <v>26.3</v>
+        <v>23.1</v>
       </c>
       <c r="D312">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>advertised_sale_listing</t>
+          <t>operating_sme</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -35422,27 +35628,27 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>Commercial &amp; Professional Services</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>live listing</t>
+          <t>verified profile</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
+          <t>CRO/profile evidence includes legal identity and trading status.</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>material new evidence</t>
+          <t>sector subsector</t>
         </is>
       </c>
       <c r="O312" t="inlineStr">
@@ -35457,73 +35663,73 @@
       </c>
       <c r="Q312" t="inlineStr">
         <is>
-          <t>ic_packs/name-county-weddingbox-event-planning-franchise-in-dublin-dublin/watch_note.md</t>
+          <t>ic_packs/cro-345282/watch_note.md</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>GARDEN GREEN ENERGY LIMITED</t>
+          <t>Young Engineers Franchise in Dublin</t>
         </is>
       </c>
       <c r="B313">
-        <v>3.8</v>
+        <v>0.0</v>
       </c>
       <c r="C313">
-        <v>25.8</v>
+        <v>23.6</v>
       </c>
       <c r="D313">
-        <v>22.0</v>
+        <v>45.0</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>watchlist_only</t>
+          <t>discard</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Keep visible but do not spend major time until better evidence appears.</t>
+          <t>Outside scope or too weak for the current origination workflow.</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>operating_sme</t>
+          <t>advertised_sale_listing</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t/>
+          <t>Business Services</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>Food, Beverage &amp; Tobacco</t>
+          <t>Cleaning &amp; facilities management</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>verified profile</t>
+          <t>live listing</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>CRO/profile evidence includes legal identity and trading status.</t>
+          <t>Broker/listing source shows transaction intent; price may still need manual confirmation.</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>sector subsector</t>
+          <t>material new evidence</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
@@ -35538,7 +35744,7 @@
       </c>
       <c r="Q313" t="inlineStr">
         <is>
-          <t>ic_packs/cro-463334/watch_note.md</t>
+          <t>ic_packs/name-county-young-engineers-franchise-in-dublin-dublin/watch_note.md</t>
         </is>
       </c>
     </row>
@@ -38026,8 +38232,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -38065,12 +38271,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t/>
+          <t>Interactive site</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t/>
+          <t>310 ranked public targets are available in the dashboard.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -38082,12 +38288,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t/>
+          <t>Live sale feed</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t/>
+          <t>226 advertised sale listings are published; 226 came from the latest public refresh.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -38099,12 +38305,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t/>
+          <t>Sector taxonomy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t/>
+          <t>15 sectors and 104 subsectors are configured; 25 subsectors currently have observed targets/listings/evidence.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -38116,12 +38322,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t/>
+          <t>Approved source rows</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t/>
+          <t>33 of 120 approved source rows are complete (27.5%).</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -38133,12 +38339,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t/>
+          <t>Company evidence gate</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t/>
+          <t>Approved company-count evidence and source metadata are required before investment decisions.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
